--- a/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1725924154968874</v>
+        <v>0.2756297397202825</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03959796054831155</v>
+        <v>0.1132957393483709</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.26%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=27.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1514851372428482</v>
+        <v>0.1718074768492039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03475530758943485</v>
+        <v>0.07062030075187975</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=15.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1492537313432844</v>
+        <v>0.1483937349948541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03424335506519549</v>
+        <v>0.06099624060150383</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=14.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1108872115395569</v>
+        <v>0.106718493959833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02544090605148774</v>
+        <v>0.0438659147869675</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=11.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=10.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1016428156699347</v>
+        <v>0.05951754887389934</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02331995987963886</v>
+        <v>0.02446428571428583</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=10.16%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.07307854321072019</v>
+        <v>0.04794786784040215</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01676644516883979</v>
+        <v>0.01970864661654143</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=7.31%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05602422669262386</v>
+        <v>0.03109637590030856</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01285366516215303</v>
+        <v>0.01278195488721812</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=3.11%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04550474173753693</v>
+        <v>0.02996837010784641</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01044017469073888</v>
+        <v>0.01231829573934845</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.00%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02871227387092019</v>
+        <v>0.02584505163675153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006587470745570034</v>
+        <v>0.01062343358395995</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.87%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02771041816091179</v>
+        <v>0.02395487976830145</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006357614510197229</v>
+        <v>0.009846491228070242</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=2.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2756297397202825</v>
+        <v>0.2662079403069144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1132957393483709</v>
+        <v>0.05426239799121152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=27.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1718074768492039</v>
+        <v>0.1355325214698025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07062030075187975</v>
+        <v>0.02762622186350999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1483937349948541</v>
+        <v>0.1189286217091377</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06099624060150383</v>
+        <v>0.02424177203838218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.106718493959833</v>
+        <v>0.06474377023792785</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0438659147869675</v>
+        <v>0.01319702268854805</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=10.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05951754887389934</v>
+        <v>0.05747571448683674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02446428571428583</v>
+        <v>0.01171554120706658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04794786784040215</v>
+        <v>0.04826305786287505</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01970864661654143</v>
+        <v>0.009837682719038621</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03109637590030856</v>
+        <v>0.03557475714486848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01278195488721812</v>
+        <v>0.00725136759035061</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=3.11%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회계연도</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.02996837010784641</v>
+        <v>0.03502921300858811</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01231829573934845</v>
+        <v>0.007140166801183734</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.00%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02584505163675153</v>
+        <v>0.03132479234126444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01062343358395995</v>
+        <v>0.006385077571518238</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02395487976830145</v>
+        <v>0.02879945093622435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009846491228070242</v>
+        <v>0.00587032553134248</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=2.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/gradient_boosting_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2662079403069144</v>
+        <v>0.1947102492449268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05426239799121152</v>
+        <v>0.06048206785892779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=19.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1355325214698025</v>
+        <v>0.1458445065439734</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02762622186350999</v>
+        <v>0.04530309717054748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=14.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1189286217091377</v>
+        <v>0.1120755356084346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02424177203838218</v>
+        <v>0.03481357646185457</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=11.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06474377023792785</v>
+        <v>0.1041060961037252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01319702268854805</v>
+        <v>0.03233806126534772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05747571448683674</v>
+        <v>0.07371025865394595</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01171554120706658</v>
+        <v>0.02289632355305116</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04826305786287505</v>
+        <v>0.04473047863682122</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009837682719038621</v>
+        <v>0.01389445011120816</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>카드해외사용건수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03557475714486848</v>
+        <v>0.04181838710588008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00725136759035061</v>
+        <v>0.01298987873775037</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 카드해외사용건수(CARD_FR_USE_CNT). 기여도(정규화 비중)=4.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03502921300858811</v>
+        <v>0.03752316971048448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007140166801183734</v>
+        <v>0.01165567249547711</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03132479234126444</v>
+        <v>0.02720617984399845</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006385077571518238</v>
+        <v>0.008450947096457384</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02879945093622435</v>
+        <v>0.02115147580470616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00587032553134248</v>
+        <v>0.00657019853807228</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
